--- a/24_DS_CLUB_BATCH1_AHM/01_Advanced Excel/Oct13.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/01_Advanced Excel/Oct13.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\24_DS_CLUB_BATCH1_AHM\01_Advanced Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\01_Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2DACF1-9A7F-4C36-97F9-DD1A8B13DF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0233B2B-BD22-4A0B-B59E-1AF3D10F51AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>Which rows have April as their month and 'Numbers' at least 10?</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Adults</t>
-  </si>
-  <si>
     <t>Day of Stay</t>
   </si>
   <si>
@@ -178,6 +175,18 @@
   </si>
   <si>
     <t>Per Capita Income</t>
+  </si>
+  <si>
+    <t>No. of seats</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Year (Full)</t>
+  </si>
+  <si>
+    <t>VLOOKUP, HLOOKUP, INDEX-MATCH</t>
   </si>
 </sst>
 </file>
@@ -207,7 +216,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +238,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -341,17 +356,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,25 +680,25 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -699,7 +716,7 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -1929,56 +1946,84 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B28AA9-963F-4813-9A2E-1F079B127A73}">
-  <dimension ref="C3:D6"/>
+  <dimension ref="B2:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
+      <c r="D3" s="18">
+        <v>7</v>
+      </c>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="18">
+        <v>3</v>
+      </c>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+      <c r="D5" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17" t="s">
         <v>24</v>
       </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Quanity!" error="Quantity can not be negative nor it can be a decimal number!" promptTitle="Non-negative Integers Only..." prompt="Please do not enter negative integers or decimal numbers." sqref="D3" xr:uid="{69908907-B7A9-43A5-9332-21A0EF46D72C}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Positive Integers Please..." error="Quantity cannot be a negative, a zero or a decimal number!" promptTitle="Rules for this cell:" prompt="We must enter a positive integer as quantity." sqref="D3" xr:uid="{7FC7065F-8FA7-472B-9DA9-73A7179D5CDB}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{477A8773-5050-4308-827F-DE86ABFAAAE0}">
-      <formula1>"1, 2, 3, 4, ,5, 6"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{3478187B-53D9-47AF-90FC-85B3BC4F445A}">
+      <formula1>"1,2,3,4,5,6"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6" xr:uid="{2355B53E-DE4B-4F25-9787-62E1E2B07E01}">
-      <formula1>"Mon, Tue, Wed, Thu, Fri, Sat, Sun"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5" xr:uid="{F7F51F22-9250-490A-9E6A-18A937037691}">
+      <formula1>"Monday, Tuesday, Wednesday, Thursday, Friday"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77E02BB2-B828-4D72-8726-20A882404B0E}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4CEE82A5-AB3F-4A45-A0E5-05350CC10A52}">
           <x14:formula1>
             <xm:f>'Oct13'!$A$3:$S$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D5</xm:sqref>
+          <xm:sqref>D6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2000,22 +2045,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
-        <v>30</v>
-      </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2023,7 +2068,7 @@
         <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>86</v>
@@ -2043,7 +2088,7 @@
         <v>261</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>80</v>
@@ -2063,7 +2108,7 @@
         <v>2766</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -2083,7 +2128,7 @@
         <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>46</v>
@@ -2103,7 +2148,7 @@
         <v>2744</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2123,7 +2168,7 @@
         <v>2742</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>1.5</v>
@@ -2145,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4C06A5F-3126-45F3-A149-8EB25C0E0C09}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -2157,62 +2202,63 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2">
-        <v>2590</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3">
-        <v>3196</v>
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B4">
-        <v>2400</v>
+        <v>2590</v>
+      </c>
+      <c r="C4">
+        <f>VLOOKUP(A4, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>68.7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>2530</v>
+        <v>3196</v>
+      </c>
+      <c r="C5">
+        <f>VLOOKUP(A5, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>68.8</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>2900</v>
+        <v>2400</v>
+      </c>
+      <c r="C6">
+        <f>VLOOKUP(A6, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>64.900000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2220,112 +2266,140 @@
         <v>32</v>
       </c>
       <c r="B7">
+        <v>2530</v>
+      </c>
+      <c r="C7">
+        <f>VLOOKUP(A7, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>2900</v>
+      </c>
+      <c r="C8">
+        <f>VLOOKUP(A8, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
         <v>2850</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="C9">
+        <f>VLOOKUP(A9, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="D13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="D11" s="11" t="s">
+      <c r="E13" s="16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12" t="s">
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="10"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="12"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="12"/>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/24_DS_CLUB_BATCH1_AHM/01_Advanced Excel/Oct13.xlsx
+++ b/24_DS_CLUB_BATCH1_AHM/01_Advanced Excel/Oct13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_CLUB_BATCH1_AHM\01_Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0233B2B-BD22-4A0B-B59E-1AF3D10F51AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936D80BF-2590-43EE-8784-C34E851A9BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>Which rows have April as their month and 'Numbers' at least 10?</t>
   </si>
@@ -150,9 +150,6 @@
     <t>Enter Index No</t>
   </si>
   <si>
-    <t>Index No</t>
-  </si>
-  <si>
     <t>Enter Row No</t>
   </si>
   <si>
@@ -187,6 +184,33 @@
   </si>
   <si>
     <t>VLOOKUP, HLOOKUP, INDEX-MATCH</t>
+  </si>
+  <si>
+    <t>Enter Field</t>
+  </si>
+  <si>
+    <t>Column No</t>
+  </si>
+  <si>
+    <t>Row No</t>
+  </si>
+  <si>
+    <t>Not Allowed</t>
+  </si>
+  <si>
+    <t>Sr.No.</t>
+  </si>
+  <si>
+    <t>Row num</t>
+  </si>
+  <si>
+    <t>Col num</t>
+  </si>
+  <si>
+    <t>STD Code (Can't get using VLOOKUP!)</t>
+  </si>
+  <si>
+    <t>Row no</t>
   </si>
 </sst>
 </file>
@@ -335,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -361,14 +385,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,18 +703,18 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -716,7 +739,7 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -1954,54 +1977,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3">
         <v>7</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="17"/>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="15"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="18">
-        <v>3</v>
-      </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="17"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2057,10 +2079,10 @@
         <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2190,7 +2212,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4C06A5F-3126-45F3-A149-8EB25C0E0C09}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -2200,146 +2222,267 @@
     <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
       <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>2590</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(B4, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>68.7</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(B4,Population!$B$1:$C$7,2,FALSE)</f>
+        <v>86</v>
+      </c>
+      <c r="F4">
+        <f>VLOOKUP(B4, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>110</v>
+      </c>
+      <c r="G4">
+        <f>INDEX(Population!A2:A7,1)</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>3196</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(B5, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>68.8</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(B5,Population!$B$1:$C$7,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <f>VLOOKUP(B5, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <f>INDEX(Population!A2:A7, J5)</f>
+        <v>2744</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5">
+        <f>MATCH(B5, Population!B2:B7, 0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>2400</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP(B6, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>64.900000000000006</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(B6,Population!$B$1:$C$7,2,FALSE)</f>
+        <v>1.5</v>
+      </c>
+      <c r="F6">
+        <f>VLOOKUP(B6, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <f>INDEX(Population!$A$2:$A$7, MATCH('Per Capita Income'!B6, Population!$B$2:$B$7, 0))</f>
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>2530</v>
+      </c>
+      <c r="D7">
+        <f>VLOOKUP(B7, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>72.3</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(B7,Population!$B$1:$C$7,2,FALSE)</f>
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <f>VLOOKUP(B7, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <f>INDEX(Population!$A$2:$A$7, MATCH('Per Capita Income'!B7, Population!$B$2:$B$7, 0))</f>
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>2900</v>
+      </c>
+      <c r="D8">
+        <f>VLOOKUP(B8, Population!$B$1:$D$7,3,FALSE)</f>
+        <v>52.2</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP(B8,Population!$B$1:$C$7,2,FALSE)</f>
         <v>46</v>
       </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4">
-        <v>2590</v>
-      </c>
-      <c r="C4">
-        <f>VLOOKUP(A4, Population!$B$1:$D$7,3,FALSE)</f>
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5">
-        <v>3196</v>
-      </c>
-      <c r="C5">
-        <f>VLOOKUP(A5, Population!$B$1:$D$7,3,FALSE)</f>
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6">
-        <v>2400</v>
-      </c>
-      <c r="C6">
-        <f>VLOOKUP(A6, Population!$B$1:$D$7,3,FALSE)</f>
-        <v>64.900000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>2530</v>
-      </c>
-      <c r="C7">
-        <f>VLOOKUP(A7, Population!$B$1:$D$7,3,FALSE)</f>
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8">
-        <v>2900</v>
-      </c>
-      <c r="C8">
-        <f>VLOOKUP(A8, Population!$B$1:$D$7,3,FALSE)</f>
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="F8">
+        <f>VLOOKUP(B8, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>45</v>
+      </c>
+      <c r="G8">
+        <f>INDEX(Population!$A$2:$A$7, MATCH('Per Capita Income'!B8, Population!$B$2:$B$7, 0))</f>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>2850</v>
       </c>
-      <c r="C9">
-        <f>VLOOKUP(A9, Population!$B$1:$D$7,3,FALSE)</f>
+      <c r="D9">
+        <f>VLOOKUP(B9, Population!$B$1:$D$7,3,FALSE)</f>
         <v>60.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+      <c r="E9">
+        <f>VLOOKUP(B9,Population!$B$1:$C$7,2,FALSE)</f>
+        <v>80</v>
+      </c>
+      <c r="F9">
+        <f>VLOOKUP(B9, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>98</v>
+      </c>
+      <c r="G9">
+        <f>INDEX(Population!$A$2:$A$7, MATCH('Per Capita Income'!B9, Population!$B$2:$B$7, 0))</f>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="D13" s="16" t="s">
+      <c r="B13" s="17"/>
+      <c r="D13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>54</v>
+      </c>
+      <c r="B18">
+        <f>MATCH(B17,B3:B9,0)</f>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
+      <c r="E18" t="str">
+        <f>INDEX(B4:B9, E17)</f>
+        <v>Surat</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
       <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21">
+        <f>MATCH(B20, B3:G3, 0)</f>
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
         <v>41</v>
-      </c>
-      <c r="E20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
-        <v>42</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2347,7 +2490,20 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="E22">
+        <f>INDEX(B4:F9, E20, E21)</f>
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="e">
+        <f>MATCH(B20, B3:G9, 0)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2355,39 +2511,62 @@
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
+      <c r="E25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25">
+        <f>MATCH(C26, B4:B9, 0)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="11"/>
+        <v>43</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="D26" s="10"/>
-      <c r="F26" s="12"/>
+      <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="12">
+        <f>MATCH(C27, B3:G3, 0)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="13"/>
+      <c r="C27" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="D27" s="10"/>
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="13"/>
+        <v>42</v>
+      </c>
+      <c r="C28" s="13">
+        <f>INDEX(B4:G9, F25, F26)</f>
+        <v>2400</v>
+      </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="C29" s="14">
+        <f>INDEX(B4:G9,MATCH(C26,B4:B9,0),MATCH(C27,B3:G3,0))</f>
+        <v>2400</v>
+      </c>
       <c r="D29" s="10"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2401,6 +2580,17 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="D13:E13"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20" xr:uid="{867F4BE0-0DDB-4120-9DD8-FF9394FB6C05}">
+      <formula1>$B$3:$G$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C26" xr:uid="{AD773BC3-526E-4C64-92C4-6C4B4EC82BEB}">
+      <formula1>$B$4:$B$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27" xr:uid="{F59ABB8A-1232-47B8-9A3A-C68781964029}">
+      <formula1>$C$3:$G$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>